--- a/Pruebas calificadas/COLEGIO FRANCISCO DE MIRANDA._301_CALIFICADO.xlsx
+++ b/Pruebas calificadas/COLEGIO FRANCISCO DE MIRANDA._301_CALIFICADO.xlsx
@@ -747,11 +747,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A2" s="2" t="inlineStr"/>
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>111001014974</t>
@@ -759,7 +755,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+          <t>FRANCISCO DE MIRANDA</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -946,11 +942,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A3" s="2" t="inlineStr"/>
       <c r="B3" s="2" t="inlineStr">
         <is>
           <t>111001014974</t>
@@ -958,7 +950,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+          <t>FRANCISCO DE MIRANDA</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -1149,11 +1141,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A4" s="2" t="inlineStr"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
           <t>111001014974</t>
@@ -1161,7 +1149,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+          <t>FRANCISCO DE MIRANDA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1352,11 +1340,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A5" s="2" t="inlineStr"/>
       <c r="B5" s="2" t="inlineStr">
         <is>
           <t>111001014974</t>
@@ -1364,7 +1348,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+          <t>FRANCISCO DE MIRANDA</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -1555,11 +1539,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A6" s="2" t="inlineStr"/>
       <c r="B6" s="2" t="inlineStr">
         <is>
           <t>111001014974</t>
@@ -1567,7 +1547,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+          <t>FRANCISCO DE MIRANDA</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1758,11 +1738,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A7" s="2" t="inlineStr"/>
       <c r="B7" s="2" t="inlineStr">
         <is>
           <t>111001014974</t>
@@ -1770,7 +1746,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+          <t>FRANCISCO DE MIRANDA</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -1961,11 +1937,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A8" s="2" t="inlineStr"/>
       <c r="B8" s="2" t="inlineStr">
         <is>
           <t>111001014974</t>
@@ -1973,7 +1945,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+          <t>FRANCISCO DE MIRANDA</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -2164,11 +2136,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A9" s="2" t="inlineStr"/>
       <c r="B9" s="2" t="inlineStr">
         <is>
           <t>111001014974</t>
@@ -2176,7 +2144,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+          <t>FRANCISCO DE MIRANDA</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2367,11 +2335,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A10" s="2" t="inlineStr"/>
       <c r="B10" s="2" t="inlineStr">
         <is>
           <t>111001014974</t>
@@ -2379,7 +2343,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+          <t>FRANCISCO DE MIRANDA</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -2550,11 +2514,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A11" s="2" t="inlineStr"/>
       <c r="B11" s="2" t="inlineStr">
         <is>
           <t>111001014974</t>
@@ -2562,7 +2522,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+          <t>FRANCISCO DE MIRANDA</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -2693,11 +2653,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A12" s="2" t="inlineStr"/>
       <c r="B12" s="2" t="inlineStr">
         <is>
           <t>111001014974</t>
@@ -2705,7 +2661,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+          <t>FRANCISCO DE MIRANDA</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -2896,11 +2852,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A13" s="2" t="inlineStr"/>
       <c r="B13" s="2" t="inlineStr">
         <is>
           <t>111001014974</t>
@@ -2908,7 +2860,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+          <t>FRANCISCO DE MIRANDA</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -3099,11 +3051,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A14" s="2" t="inlineStr"/>
       <c r="B14" s="2" t="inlineStr">
         <is>
           <t>111001014974</t>
@@ -3111,7 +3059,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+          <t>FRANCISCO DE MIRANDA</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -3302,11 +3250,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A15" s="2" t="inlineStr"/>
       <c r="B15" s="2" t="inlineStr">
         <is>
           <t>111001014974</t>
@@ -3314,7 +3258,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+          <t>FRANCISCO DE MIRANDA</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -3505,11 +3449,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A16" s="2" t="inlineStr"/>
       <c r="B16" s="2" t="inlineStr">
         <is>
           <t>111001014974</t>
@@ -3517,7 +3457,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+          <t>FRANCISCO DE MIRANDA</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -3708,11 +3648,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A17" s="2" t="inlineStr"/>
       <c r="B17" s="2" t="inlineStr">
         <is>
           <t>111001014974</t>
@@ -3720,7 +3656,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+          <t>FRANCISCO DE MIRANDA</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -3911,11 +3847,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A18" s="2" t="inlineStr"/>
       <c r="B18" s="2" t="inlineStr">
         <is>
           <t>111001014974</t>
@@ -3923,7 +3855,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+          <t>FRANCISCO DE MIRANDA</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -4106,11 +4038,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A19" s="2" t="inlineStr"/>
       <c r="B19" s="2" t="inlineStr">
         <is>
           <t>111001014974</t>
@@ -4118,7 +4046,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+          <t>FRANCISCO DE MIRANDA</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -4309,11 +4237,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A20" s="2" t="inlineStr"/>
       <c r="B20" s="2" t="inlineStr">
         <is>
           <t>111001014974</t>
@@ -4321,7 +4245,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+          <t>FRANCISCO DE MIRANDA</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -4512,11 +4436,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A21" s="2" t="inlineStr"/>
       <c r="B21" s="2" t="inlineStr">
         <is>
           <t>111001014974</t>
@@ -4524,7 +4444,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+          <t>FRANCISCO DE MIRANDA</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -4715,11 +4635,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A22" s="2" t="inlineStr"/>
       <c r="B22" s="2" t="inlineStr">
         <is>
           <t>111001014974</t>
@@ -4727,7 +4643,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+          <t>FRANCISCO DE MIRANDA</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -4918,11 +4834,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A23" s="2" t="inlineStr"/>
       <c r="B23" s="2" t="inlineStr">
         <is>
           <t>111001014974</t>
@@ -4930,7 +4842,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+          <t>FRANCISCO DE MIRANDA</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -5121,11 +5033,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A24" s="2" t="inlineStr"/>
       <c r="B24" s="2" t="inlineStr">
         <is>
           <t>111001014974</t>
@@ -5133,7 +5041,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+          <t>FRANCISCO DE MIRANDA</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -5324,11 +5232,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A25" s="2" t="inlineStr"/>
       <c r="B25" s="2" t="inlineStr">
         <is>
           <t>111001014974</t>
@@ -5336,7 +5240,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+          <t>FRANCISCO DE MIRANDA</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -5527,11 +5431,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A26" s="2" t="inlineStr"/>
       <c r="B26" s="2" t="inlineStr">
         <is>
           <t>111001014974</t>
@@ -5539,7 +5439,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+          <t>FRANCISCO DE MIRANDA</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -5730,11 +5630,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A27" s="2" t="inlineStr"/>
       <c r="B27" s="2" t="inlineStr">
         <is>
           <t>111001014974</t>
@@ -5742,7 +5638,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+          <t>FRANCISCO DE MIRANDA</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -5873,11 +5769,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A28" s="2" t="inlineStr"/>
       <c r="B28" s="2" t="inlineStr">
         <is>
           <t>111001014974</t>
@@ -5885,7 +5777,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+          <t>FRANCISCO DE MIRANDA</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -6076,11 +5968,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A29" s="2" t="inlineStr"/>
       <c r="B29" s="2" t="inlineStr">
         <is>
           <t>111001014974</t>
@@ -6088,7 +5976,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+          <t>FRANCISCO DE MIRANDA</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -6279,11 +6167,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A30" s="2" t="inlineStr"/>
       <c r="B30" s="2" t="inlineStr">
         <is>
           <t>111001014974</t>
@@ -6291,7 +6175,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+          <t>FRANCISCO DE MIRANDA</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -6482,11 +6366,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A31" s="2" t="inlineStr"/>
       <c r="B31" s="2" t="inlineStr">
         <is>
           <t>111001014974</t>
@@ -6494,7 +6374,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+          <t>FRANCISCO DE MIRANDA</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -6685,11 +6565,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A32" s="2" t="inlineStr"/>
       <c r="B32" s="2" t="inlineStr">
         <is>
           <t>111001014974</t>
@@ -6697,7 +6573,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+          <t>FRANCISCO DE MIRANDA</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -6888,11 +6764,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A33" s="2" t="inlineStr"/>
       <c r="B33" s="2" t="inlineStr">
         <is>
           <t>111001014974</t>
@@ -6900,7 +6772,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+          <t>FRANCISCO DE MIRANDA</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -7091,11 +6963,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A34" s="2" t="inlineStr"/>
       <c r="B34" s="2" t="inlineStr">
         <is>
           <t>111001014974</t>
@@ -7103,7 +6971,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+          <t>FRANCISCO DE MIRANDA</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -7294,11 +7162,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A35" s="2" t="inlineStr"/>
       <c r="B35" s="2" t="inlineStr">
         <is>
           <t>111001014974</t>
@@ -7306,7 +7170,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+          <t>FRANCISCO DE MIRANDA</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -7493,11 +7357,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A36" s="2" t="inlineStr"/>
       <c r="B36" s="2" t="inlineStr">
         <is>
           <t>111001014974</t>
@@ -7505,7 +7365,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+          <t>FRANCISCO DE MIRANDA</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -7696,11 +7556,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A37" s="2" t="inlineStr"/>
       <c r="B37" s="2" t="inlineStr">
         <is>
           <t>111001014974</t>
@@ -7708,7 +7564,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+          <t>FRANCISCO DE MIRANDA</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -7899,11 +7755,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A38" s="2" t="inlineStr"/>
       <c r="B38" s="2" t="inlineStr">
         <is>
           <t>111001014974</t>
@@ -7911,7 +7763,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+          <t>FRANCISCO DE MIRANDA</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -8102,11 +7954,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A39" s="2" t="inlineStr"/>
       <c r="B39" s="2" t="inlineStr">
         <is>
           <t>111001014974</t>
@@ -8114,7 +7962,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+          <t>FRANCISCO DE MIRANDA</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -8305,11 +8153,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A40" s="2" t="inlineStr"/>
       <c r="B40" s="2" t="inlineStr">
         <is>
           <t>111001014974</t>
@@ -8317,7 +8161,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+          <t>FRANCISCO DE MIRANDA</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -8508,11 +8352,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A41" s="2" t="inlineStr"/>
       <c r="B41" s="2" t="inlineStr">
         <is>
           <t>111001014974</t>
@@ -8520,7 +8360,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+          <t>FRANCISCO DE MIRANDA</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -8707,11 +8547,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A42" s="2" t="inlineStr"/>
       <c r="B42" s="2" t="inlineStr">
         <is>
           <t>111001014974</t>
@@ -8719,7 +8555,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+          <t>FRANCISCO DE MIRANDA</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -8910,11 +8746,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A43" s="2" t="inlineStr"/>
       <c r="B43" s="2" t="inlineStr">
         <is>
           <t>111001014974</t>
@@ -8922,7 +8754,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+          <t>FRANCISCO DE MIRANDA</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -9113,11 +8945,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A44" s="2" t="inlineStr"/>
       <c r="B44" s="2" t="inlineStr">
         <is>
           <t>111001014974</t>
@@ -9125,7 +8953,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+          <t>FRANCISCO DE MIRANDA</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -9316,11 +9144,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A45" s="2" t="inlineStr"/>
       <c r="B45" s="2" t="inlineStr">
         <is>
           <t>111001014974</t>
@@ -9328,7 +9152,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+          <t>FRANCISCO DE MIRANDA</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -9519,11 +9343,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A46" s="2" t="inlineStr"/>
       <c r="B46" s="2" t="inlineStr">
         <is>
           <t>111001014974</t>
@@ -9531,7 +9351,7 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+          <t>FRANCISCO DE MIRANDA</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -9722,11 +9542,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A47" s="2" t="inlineStr"/>
       <c r="B47" s="2" t="inlineStr">
         <is>
           <t>111001014974</t>
@@ -9734,7 +9550,7 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+          <t>FRANCISCO DE MIRANDA</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -9925,11 +9741,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A48" s="2" t="inlineStr"/>
       <c r="B48" s="2" t="inlineStr">
         <is>
           <t>111001014974</t>
@@ -9937,7 +9749,7 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+          <t>FRANCISCO DE MIRANDA</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -10128,11 +9940,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A49" s="2" t="inlineStr"/>
       <c r="B49" s="2" t="inlineStr">
         <is>
           <t>111001014974</t>
@@ -10140,7 +9948,7 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+          <t>FRANCISCO DE MIRANDA</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -10331,11 +10139,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A50" s="2" t="inlineStr"/>
       <c r="B50" s="2" t="inlineStr">
         <is>
           <t>111001014974</t>
@@ -10343,7 +10147,7 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+          <t>FRANCISCO DE MIRANDA</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -10534,11 +10338,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A51" s="2" t="inlineStr"/>
       <c r="B51" s="2" t="inlineStr">
         <is>
           <t>111001014974</t>
@@ -10546,7 +10346,7 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+          <t>FRANCISCO DE MIRANDA</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -10737,11 +10537,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A52" s="2" t="inlineStr"/>
       <c r="B52" s="2" t="inlineStr">
         <is>
           <t>111001014974</t>
@@ -10749,7 +10545,7 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+          <t>FRANCISCO DE MIRANDA</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -10936,11 +10732,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A53" s="2" t="inlineStr"/>
       <c r="B53" s="2" t="inlineStr">
         <is>
           <t>111001014974</t>
@@ -10948,7 +10740,7 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+          <t>FRANCISCO DE MIRANDA</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -11131,11 +10923,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A54" s="2" t="inlineStr"/>
       <c r="B54" s="2" t="inlineStr">
         <is>
           <t>111001014974</t>
@@ -11143,7 +10931,7 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+          <t>FRANCISCO DE MIRANDA</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -11318,11 +11106,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A55" s="2" t="inlineStr"/>
       <c r="B55" s="2" t="inlineStr">
         <is>
           <t>111001014974</t>
@@ -11330,7 +11114,7 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+          <t>FRANCISCO DE MIRANDA</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -11521,11 +11305,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A56" s="2" t="inlineStr"/>
       <c r="B56" s="2" t="inlineStr">
         <is>
           <t>111001014974</t>
@@ -11533,7 +11313,7 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+          <t>FRANCISCO DE MIRANDA</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -11720,11 +11500,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A57" s="2" t="inlineStr"/>
       <c r="B57" s="2" t="inlineStr">
         <is>
           <t>111001014974</t>
@@ -11732,7 +11508,7 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO FRANCISCO DE MIRANDA (IED)</t>
+          <t>FRANCISCO DE MIRANDA</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
